--- a/results/canaliculi/542_WT__2_z18c1-2/measurements.xlsx
+++ b/results/canaliculi/542_WT__2_z18c1-2/measurements.xlsx
@@ -441,10 +441,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4">
@@ -493,13 +493,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>50.25</v>
+        <v>55.0909</v>
       </c>
       <c r="C6" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="D6" t="n">
-        <v>29.3075</v>
+        <v>28.5568</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
@@ -517,13 +517,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>175.8981</v>
+        <v>190.7962</v>
       </c>
       <c r="C7" t="n">
-        <v>167.8085</v>
+        <v>176.1539</v>
       </c>
       <c r="D7" t="n">
-        <v>58.1905</v>
+        <v>59.158</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -545,7 +545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -761,13 +761,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="C10" t="n">
-        <v>7134.4393</v>
+        <v>16380.9375</v>
       </c>
       <c r="D10" t="n">
-        <v>216.1951</v>
+        <v>282.43</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
@@ -783,13 +783,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>1721.5799</v>
+        <v>3594.8826</v>
       </c>
       <c r="D11" t="n">
-        <v>78.25360000000001</v>
+        <v>128.3887</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>
@@ -805,13 +805,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>3594.8826</v>
+        <v>2803.1799</v>
       </c>
       <c r="D12" t="n">
-        <v>128.3887</v>
+        <v>116.7992</v>
       </c>
       <c r="E12" t="b">
         <v>0</v>
@@ -827,40 +827,18 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>24</v>
+        <v>75</v>
       </c>
       <c r="C13" t="n">
-        <v>2803.1799</v>
+        <v>14164.054</v>
       </c>
       <c r="D13" t="n">
-        <v>116.7992</v>
+        <v>188.8541</v>
       </c>
       <c r="E13" t="b">
         <v>0</v>
       </c>
       <c r="F13" t="inlineStr">
-        <is>
-          <t>px</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" t="n">
-        <v>75</v>
-      </c>
-      <c r="C14" t="n">
-        <v>14164.054</v>
-      </c>
-      <c r="D14" t="n">
-        <v>188.8541</v>
-      </c>
-      <c r="E14" t="b">
-        <v>0</v>
-      </c>
-      <c r="F14" t="inlineStr">
         <is>
           <t>px</t>
         </is>

--- a/results/canaliculi/542_WT__2_z18c1-2/measurements.xlsx
+++ b/results/canaliculi/542_WT__2_z18c1-2/measurements.xlsx
@@ -433,6 +433,11 @@
           <t>interior_lacuna_count</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>assignment_method</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -446,6 +451,11 @@
       <c r="C2" t="n">
         <v>11</v>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>graph</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -493,13 +503,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>55.0909</v>
+        <v>42.3636</v>
       </c>
       <c r="C6" t="n">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="D6" t="n">
-        <v>28.5568</v>
+        <v>34.9064</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -517,13 +527,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>190.7962</v>
+        <v>107.7262</v>
       </c>
       <c r="C7" t="n">
-        <v>176.1539</v>
+        <v>86.01900000000001</v>
       </c>
       <c r="D7" t="n">
-        <v>59.158</v>
+        <v>57.7495</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -585,13 +595,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="C2" t="n">
-        <v>3105.6623</v>
+        <v>1436.4844</v>
       </c>
       <c r="D2" t="n">
-        <v>135.0288</v>
+        <v>89.7803</v>
       </c>
       <c r="E2" t="b">
         <v>1</v>
@@ -607,13 +617,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>126</v>
+        <v>144</v>
       </c>
       <c r="C3" t="n">
-        <v>37322.9064</v>
+        <v>35166.3166</v>
       </c>
       <c r="D3" t="n">
-        <v>296.2135</v>
+        <v>244.2105</v>
       </c>
       <c r="E3" t="b">
         <v>0</v>
@@ -629,13 +639,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C4" t="n">
-        <v>9934.9746</v>
+        <v>6636.2484</v>
       </c>
       <c r="D4" t="n">
-        <v>215.9777</v>
+        <v>147.4722</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
@@ -651,13 +661,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="C5" t="n">
-        <v>8132.6201</v>
+        <v>2868.8633</v>
       </c>
       <c r="D5" t="n">
-        <v>159.4631</v>
+        <v>73.56059999999999</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
@@ -673,13 +683,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="C6" t="n">
-        <v>11649.7677</v>
+        <v>4332.8969</v>
       </c>
       <c r="D6" t="n">
-        <v>228.4268</v>
+        <v>123.7971</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
@@ -695,13 +705,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="C7" t="n">
-        <v>5758.1975</v>
+        <v>2666.5891</v>
       </c>
       <c r="D7" t="n">
-        <v>155.627</v>
+        <v>86.01900000000001</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
@@ -717,13 +727,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>72</v>
+        <v>43</v>
       </c>
       <c r="C8" t="n">
-        <v>12683.0814</v>
+        <v>3413.6795</v>
       </c>
       <c r="D8" t="n">
-        <v>176.1539</v>
+        <v>79.3879</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
@@ -739,13 +749,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="C9" t="n">
-        <v>5716.1193</v>
+        <v>1935.1413</v>
       </c>
       <c r="D9" t="n">
-        <v>150.4242</v>
+        <v>66.729</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
@@ -761,13 +771,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>16380.9375</v>
+        <v>5448.5945</v>
       </c>
       <c r="D10" t="n">
-        <v>282.43</v>
+        <v>143.3841</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
@@ -783,13 +793,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="C11" t="n">
-        <v>3594.8826</v>
+        <v>1128.9504</v>
       </c>
       <c r="D11" t="n">
-        <v>128.3887</v>
+        <v>62.7195</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>
@@ -805,13 +815,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>2803.1799</v>
+        <v>635.0315000000001</v>
       </c>
       <c r="D12" t="n">
-        <v>116.7992</v>
+        <v>35.2795</v>
       </c>
       <c r="E12" t="b">
         <v>0</v>
@@ -827,13 +837,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>75</v>
+        <v>26</v>
       </c>
       <c r="C13" t="n">
-        <v>14164.054</v>
+        <v>3183.1576</v>
       </c>
       <c r="D13" t="n">
-        <v>188.8541</v>
+        <v>122.4291</v>
       </c>
       <c r="E13" t="b">
         <v>0</v>

--- a/results/canaliculi/542_WT__2_z18c1-2/measurements.xlsx
+++ b/results/canaliculi/542_WT__2_z18c1-2/measurements.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,6 +438,16 @@
           <t>assignment_method</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>count_mode</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>preprocess_mode</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -456,91 +466,132 @@
           <t>graph</t>
         </is>
       </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>tophat</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>v1-raw / pre-validation -- stats below over interior (on_border=False) lacunae only</t>
+          <t>count_mode='edge': one canaliculus = one graph edge (OCY-style); 'path': one canaliculus = one cell-to-tip path (re-counts shared trunks)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>metric</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>mean</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>median</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>sd</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>units</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>n</t>
+          <t>v1-raw / pre-validation -- stats below over interior (on_border=False) lacunae only</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>canaliculi_count</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>42.3636</v>
-      </c>
-      <c r="C6" t="n">
-        <v>35</v>
-      </c>
-      <c r="D6" t="n">
-        <v>34.9064</v>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>median</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>sd</t>
+        </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>unitless</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>11</v>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>canaliculi_count</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>21.0909</v>
+      </c>
+      <c r="C7" t="n">
+        <v>10</v>
+      </c>
+      <c r="D7" t="n">
+        <v>17.6774</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>unitless</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>total_length_px</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>675.4888999999999</v>
+      </c>
+      <c r="C8" t="n">
+        <v>583.1737000000001</v>
+      </c>
+      <c r="D8" t="n">
+        <v>526.5481</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>mean_canaliculus_length_px</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>107.7262</v>
-      </c>
-      <c r="C7" t="n">
-        <v>86.01900000000001</v>
-      </c>
-      <c r="D7" t="n">
-        <v>57.7495</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>px</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
+      <c r="B9" t="n">
+        <v>32.6754</v>
+      </c>
+      <c r="C9" t="n">
+        <v>30.6054</v>
+      </c>
+      <c r="D9" t="n">
+        <v>13.935</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
         <v>11</v>
       </c>
     </row>
@@ -595,13 +646,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C2" t="n">
-        <v>1436.4844</v>
+        <v>256.8944</v>
       </c>
       <c r="D2" t="n">
-        <v>89.7803</v>
+        <v>19.7611</v>
       </c>
       <c r="E2" t="b">
         <v>1</v>
@@ -617,13 +668,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>144</v>
+        <v>59</v>
       </c>
       <c r="C3" t="n">
-        <v>35166.3166</v>
+        <v>1655.6631</v>
       </c>
       <c r="D3" t="n">
-        <v>244.2105</v>
+        <v>28.0621</v>
       </c>
       <c r="E3" t="b">
         <v>0</v>
@@ -639,13 +690,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="C4" t="n">
-        <v>6636.2484</v>
+        <v>583.1737000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>147.4722</v>
+        <v>58.3174</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
@@ -661,13 +712,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C5" t="n">
-        <v>2868.8633</v>
+        <v>1518.8225</v>
       </c>
       <c r="D5" t="n">
-        <v>73.56059999999999</v>
+        <v>36.1624</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
@@ -683,13 +734,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="C6" t="n">
-        <v>4332.8969</v>
+        <v>260.7939</v>
       </c>
       <c r="D6" t="n">
-        <v>123.7971</v>
+        <v>26.0794</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
@@ -705,13 +756,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C7" t="n">
-        <v>2666.5891</v>
+        <v>856.9503999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>86.01900000000001</v>
+        <v>30.6054</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
@@ -727,13 +778,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="C8" t="n">
-        <v>3413.6795</v>
+        <v>809.5534</v>
       </c>
       <c r="D8" t="n">
-        <v>79.3879</v>
+        <v>26.1146</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
@@ -749,13 +800,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>1935.1413</v>
+        <v>415.9777</v>
       </c>
       <c r="D9" t="n">
-        <v>66.729</v>
+        <v>51.9972</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
@@ -771,13 +822,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="C10" t="n">
-        <v>5448.5945</v>
+        <v>159.1249</v>
       </c>
       <c r="D10" t="n">
-        <v>143.3841</v>
+        <v>22.7321</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
@@ -793,13 +844,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>1128.9504</v>
+        <v>784.1981</v>
       </c>
       <c r="D11" t="n">
-        <v>62.7195</v>
+        <v>31.3679</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>
@@ -815,13 +866,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="C12" t="n">
-        <v>635.0315000000001</v>
+        <v>363.2203</v>
       </c>
       <c r="D12" t="n">
-        <v>35.2795</v>
+        <v>40.3578</v>
       </c>
       <c r="E12" t="b">
         <v>0</v>
@@ -837,13 +888,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>3183.1576</v>
+        <v>22.8995</v>
       </c>
       <c r="D13" t="n">
-        <v>122.4291</v>
+        <v>7.6332</v>
       </c>
       <c r="E13" t="b">
         <v>0</v>

--- a/results/canaliculi/542_WT__2_z18c1-2/measurements.xlsx
+++ b/results/canaliculi/542_WT__2_z18c1-2/measurements.xlsx
@@ -8,7 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="per_lacuna" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="field" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="per_lacuna" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -530,13 +531,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>21.0909</v>
+        <v>32</v>
       </c>
       <c r="C7" t="n">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="D7" t="n">
-        <v>17.6774</v>
+        <v>17.2743</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -554,13 +555,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>675.4888999999999</v>
+        <v>972.6153</v>
       </c>
       <c r="C8" t="n">
-        <v>583.1737000000001</v>
+        <v>961.4773</v>
       </c>
       <c r="D8" t="n">
-        <v>526.5481</v>
+        <v>477.4357</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -578,13 +579,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>32.6754</v>
+        <v>30.7951</v>
       </c>
       <c r="C9" t="n">
-        <v>30.6054</v>
+        <v>31.5344</v>
       </c>
       <c r="D9" t="n">
-        <v>13.935</v>
+        <v>5.1473</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -606,6 +607,206 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>per-field metrics -- independent of the per-lacuna assignment</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Only ~23% of skeleton length is graph-connected to any lacuna in these 2D</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>sections, so per-cell numbers use a quarter of the network. These use all of it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>analysed_area_px2</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1007403</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>total_skeleton_length_px</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>34325</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>canalicular_length_density_per_px</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.03407276</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>px^-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>junction_count</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>395</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>unitless</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>junction_density_per_px2</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.0003921</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>px^-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>lacuna_count</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>12</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>unitless</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>lacunae_per_px2</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1.191e-05</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>px^-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>skeleton_component_count</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>663</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>unitless</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>mean_component_length_px</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>51.7722</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>median_component_length_px</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>21</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -646,13 +847,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="C2" t="n">
-        <v>256.8944</v>
+        <v>586.6884</v>
       </c>
       <c r="D2" t="n">
-        <v>19.7611</v>
+        <v>22.5649</v>
       </c>
       <c r="E2" t="b">
         <v>1</v>
@@ -668,13 +869,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="C3" t="n">
-        <v>1655.6631</v>
+        <v>1962.1139</v>
       </c>
       <c r="D3" t="n">
-        <v>28.0621</v>
+        <v>26.8783</v>
       </c>
       <c r="E3" t="b">
         <v>0</v>
@@ -690,13 +891,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="C4" t="n">
-        <v>583.1737000000001</v>
+        <v>1073.3646</v>
       </c>
       <c r="D4" t="n">
-        <v>58.3174</v>
+        <v>32.5262</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
@@ -712,13 +913,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="C5" t="n">
-        <v>1518.8225</v>
+        <v>961.4773</v>
       </c>
       <c r="D5" t="n">
-        <v>36.1624</v>
+        <v>41.8034</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
@@ -734,13 +935,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C6" t="n">
-        <v>260.7939</v>
+        <v>290.3503</v>
       </c>
       <c r="D6" t="n">
-        <v>26.0794</v>
+        <v>24.1959</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
@@ -756,13 +957,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="C7" t="n">
-        <v>856.9503999999999</v>
+        <v>1513.6509</v>
       </c>
       <c r="D7" t="n">
-        <v>30.6054</v>
+        <v>31.5344</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
@@ -778,13 +979,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="C8" t="n">
-        <v>809.5534</v>
+        <v>928.9503999999999</v>
       </c>
       <c r="D8" t="n">
-        <v>26.1146</v>
+        <v>25.1068</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
@@ -800,13 +1001,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="C9" t="n">
-        <v>415.9777</v>
+        <v>1068.1514</v>
       </c>
       <c r="D9" t="n">
-        <v>51.9972</v>
+        <v>32.3682</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
@@ -822,13 +1023,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="C10" t="n">
-        <v>159.1249</v>
+        <v>457.3036</v>
       </c>
       <c r="D10" t="n">
-        <v>22.7321</v>
+        <v>26.9002</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
@@ -844,13 +1045,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C11" t="n">
-        <v>784.1981</v>
+        <v>1149.7199</v>
       </c>
       <c r="D11" t="n">
-        <v>31.3679</v>
+        <v>32.8491</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>
@@ -866,13 +1067,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>363.2203</v>
+        <v>570.4874</v>
       </c>
       <c r="D12" t="n">
-        <v>40.3578</v>
+        <v>35.6555</v>
       </c>
       <c r="E12" t="b">
         <v>0</v>
@@ -888,13 +1089,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="C13" t="n">
-        <v>22.8995</v>
+        <v>723.1981</v>
       </c>
       <c r="D13" t="n">
-        <v>7.6332</v>
+        <v>28.9279</v>
       </c>
       <c r="E13" t="b">
         <v>0</v>
